--- a/rules/CORE-000289/positive/01/data/unit-test-coreid-CG0181-positive.xlsx
+++ b/rules/CORE-000289/positive/01/data/unit-test-coreid-CG0181-positive.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="64">
   <si>
     <t>Product</t>
   </si>
@@ -130,12 +130,15 @@
     <t>LB</t>
   </si>
   <si>
+    <t>Xyz01</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>ALB</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Albumin</t>
   </si>
   <si>
@@ -151,9 +154,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Prot</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -179,6 +179,36 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>&lt;30</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>-30</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&gt;-35.55</t>
+  </si>
+  <si>
+    <t>POSITIVE</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>-35.55</t>
+  </si>
+  <si>
+    <t>&lt; 30</t>
   </si>
 </sst>
 </file>
@@ -217,7 +247,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,7 +256,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -236,14 +266,8 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="14"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -253,28 +277,28 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="11"/>
@@ -313,22 +337,37 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="13"/>
@@ -337,7 +376,7 @@
         <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -358,13 +397,13 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="11"/>
@@ -373,31 +412,46 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -407,20 +461,20 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -441,11 +495,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
@@ -453,40 +510,43 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -506,12 +566,11 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffb2b2b2"/>
       <rgbColor rgb="ffffffcc"/>
       <rgbColor rgb="ff9bbb59"/>
-      <rgbColor rgb="ffeaf1dd"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -662,9 +721,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -744,7 +803,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -771,10 +830,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1021,9 +1080,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -1301,7 +1360,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1328,10 +1387,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1765,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="13" width="8.85156" style="6" customWidth="1"/>
@@ -1946,75 +2005,75 @@
       <c r="C5" t="s" s="13">
         <v>37</v>
       </c>
-      <c r="D5" t="s" s="13">
+      <c r="D5" t="s" s="14">
         <v>38</v>
       </c>
-      <c r="E5" t="s" s="13">
+      <c r="E5" t="s" s="14">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="14">
+        <v>40</v>
+      </c>
+      <c r="G5" s="15">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s" s="14">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s" s="14">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="14">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="14">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s" s="16">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="17">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="39.55" customHeight="1">
+      <c r="A6" s="18">
+        <v>123101</v>
+      </c>
+      <c r="B6" t="s" s="19">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s" s="14">
         <v>37</v>
       </c>
-      <c r="F5" t="s" s="13">
-        <v>39</v>
-      </c>
-      <c r="G5" s="14">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s" s="13">
-        <v>40</v>
-      </c>
-      <c r="I5" t="s" s="13">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s" s="13">
-        <v>41</v>
-      </c>
-      <c r="K5" t="s" s="13">
-        <v>40</v>
-      </c>
-      <c r="L5" t="s" s="15">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s" s="16">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" ht="39.55" customHeight="1">
-      <c r="A6" s="17">
-        <v>123101</v>
-      </c>
-      <c r="B6" t="s" s="18">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s" s="19">
-        <v>44</v>
-      </c>
-      <c r="D6" t="s" s="19">
+      <c r="D6" t="s" s="20">
         <v>45</v>
       </c>
-      <c r="E6" t="s" s="19">
+      <c r="E6" t="s" s="20">
         <v>46</v>
       </c>
-      <c r="F6" t="s" s="19">
+      <c r="F6" t="s" s="20">
         <v>47</v>
       </c>
-      <c r="G6" t="s" s="19">
+      <c r="G6" t="s" s="20">
         <v>48</v>
       </c>
-      <c r="H6" t="s" s="19">
+      <c r="H6" t="s" s="20">
         <v>49</v>
       </c>
-      <c r="I6" t="s" s="19">
+      <c r="I6" t="s" s="20">
         <v>48</v>
       </c>
-      <c r="J6" t="s" s="19">
+      <c r="J6" t="s" s="20">
         <v>48</v>
       </c>
-      <c r="K6" t="s" s="19">
+      <c r="K6" t="s" s="20">
         <v>49</v>
       </c>
-      <c r="L6" t="s" s="20">
+      <c r="L6" t="s" s="21">
         <v>50</v>
       </c>
-      <c r="M6" t="s" s="21">
+      <c r="M6" t="s" s="17">
         <v>51</v>
       </c>
     </row>
@@ -2025,35 +2084,35 @@
       <c r="B7" t="s" s="12">
         <v>36</v>
       </c>
-      <c r="C7" t="s" s="13">
+      <c r="C7" t="s" s="20">
         <v>37</v>
       </c>
-      <c r="D7" t="s" s="13">
+      <c r="D7" t="s" s="14">
         <v>52</v>
       </c>
-      <c r="E7" t="s" s="13">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s" s="13">
+      <c r="E7" t="s" s="14">
         <v>39</v>
       </c>
+      <c r="F7" t="s" s="14">
+        <v>40</v>
+      </c>
       <c r="G7" s="22"/>
-      <c r="H7" t="s" s="13">
-        <v>40</v>
-      </c>
-      <c r="I7" t="s" s="13">
+      <c r="H7" t="s" s="14">
         <v>41</v>
       </c>
-      <c r="J7" t="s" s="13">
+      <c r="I7" t="s" s="14">
+        <v>42</v>
+      </c>
+      <c r="J7" t="s" s="14">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s" s="14">
         <v>41</v>
       </c>
-      <c r="K7" t="s" s="13">
-        <v>40</v>
-      </c>
-      <c r="L7" t="s" s="15">
-        <v>42</v>
-      </c>
-      <c r="M7" s="16"/>
+      <c r="L7" t="s" s="16">
+        <v>43</v>
+      </c>
+      <c r="M7" s="17"/>
     </row>
     <row r="8" ht="39.55" customHeight="1">
       <c r="A8" s="23">
@@ -2062,8 +2121,8 @@
       <c r="B8" t="s" s="4">
         <v>36</v>
       </c>
-      <c r="C8" t="s" s="24">
-        <v>44</v>
+      <c r="C8" t="s" s="14">
+        <v>37</v>
       </c>
       <c r="D8" t="s" s="24">
         <v>53</v>
@@ -2090,37 +2149,212 @@
       <c r="L8" t="s" s="25">
         <v>50</v>
       </c>
-      <c r="M8" s="21"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="26"/>
+      <c r="A9" s="26">
+        <v>123101</v>
+      </c>
+      <c r="B9" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s" s="4">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s" s="4">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="J9" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="L9" t="s" s="4">
+        <v>43</v>
+      </c>
+      <c r="M9" t="s" s="27">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="A10" s="26">
+        <v>123101</v>
+      </c>
+      <c r="B10" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s" s="4">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="J10" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="L10" t="s" s="4">
+        <v>43</v>
+      </c>
+      <c r="M10" t="s" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" ht="13.55" customHeight="1">
+      <c r="A11" s="26">
+        <v>123101</v>
+      </c>
+      <c r="B11" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="I11" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="J11" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="K11" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="L11" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="M11" t="s" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" ht="13.55" customHeight="1">
+      <c r="A12" s="26">
+        <v>123101</v>
+      </c>
+      <c r="B12" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="G12" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="H12" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="J12" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="K12" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="L12" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="M12" t="s" s="28">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="13.55" customHeight="1">
+      <c r="A13" s="26">
+        <v>123101</v>
+      </c>
+      <c r="B13" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s" s="4">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="I13" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="J13" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K13" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="L13" t="s" s="4">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s" s="27">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
